--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.12773248013383</v>
+        <v>3.920756528021747</v>
       </c>
       <c r="D2" t="n">
-        <v>24.1606665054662</v>
+        <v>3.926108307138257</v>
       </c>
       <c r="E2" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F2" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.88233407880648</v>
+        <v>5.668379287806053</v>
       </c>
       <c r="D3" t="n">
-        <v>12.03674828918531</v>
+        <v>1.955971596992613</v>
       </c>
       <c r="E3" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F3" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.96395024959268</v>
+        <v>3.731641915558811</v>
       </c>
       <c r="D4" t="n">
-        <v>14.64690674629383</v>
+        <v>2.380122346272748</v>
       </c>
       <c r="E4" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F4" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.454250674846351</v>
+        <v>1.373815734662532</v>
       </c>
       <c r="D5" t="n">
-        <v>7.976667895292228</v>
+        <v>1.296208532984987</v>
       </c>
       <c r="E5" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F5" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.59961485805959</v>
+        <v>2.372437414434683</v>
       </c>
       <c r="D6" t="n">
-        <v>14.77155829964413</v>
+        <v>2.400378223692172</v>
       </c>
       <c r="E6" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F6" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.34903258483061</v>
+        <v>4.281717795034974</v>
       </c>
       <c r="D7" t="n">
-        <v>24.85566581272388</v>
+        <v>4.039045694567632</v>
       </c>
       <c r="E7" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F7" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.81956022422145</v>
+        <v>3.220678536435986</v>
       </c>
       <c r="D8" t="n">
-        <v>20.00321140882837</v>
+        <v>3.25052185393461</v>
       </c>
       <c r="E8" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F8" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.23611835310986</v>
+        <v>4.588369232380352</v>
       </c>
       <c r="D9" t="n">
-        <v>27.90762790797496</v>
+        <v>4.534989535045931</v>
       </c>
       <c r="E9" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F9" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.4297912140892</v>
+        <v>4.457341072289495</v>
       </c>
       <c r="D10" t="n">
-        <v>28.58271399839801</v>
+        <v>4.644691024739677</v>
       </c>
       <c r="E10" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F10" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.09913978094927</v>
+        <v>3.103610214404256</v>
       </c>
       <c r="D11" t="n">
-        <v>17.85885495838813</v>
+        <v>2.902063930738071</v>
       </c>
       <c r="E11" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F11" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>54.42012147447871</v>
+        <v>8.843269739602791</v>
       </c>
       <c r="D12" t="n">
-        <v>53.11532892294127</v>
+        <v>8.631240949977958</v>
       </c>
       <c r="E12" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F12" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>41.84313518943004</v>
+        <v>6.799509468282382</v>
       </c>
       <c r="D13" t="n">
-        <v>42.29559574811177</v>
+        <v>6.873034309068162</v>
       </c>
       <c r="E13" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F13" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.78486351392031</v>
+        <v>6.46504032101205</v>
       </c>
       <c r="D14" t="n">
-        <v>38.84554741540032</v>
+        <v>6.312401455002552</v>
       </c>
       <c r="E14" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F14" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.11777516036342</v>
+        <v>6.356638463559056</v>
       </c>
       <c r="D15" t="n">
-        <v>38.63348480784661</v>
+        <v>6.277941281275075</v>
       </c>
       <c r="E15" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F15" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>47.54533655279447</v>
+        <v>7.726117189829101</v>
       </c>
       <c r="D16" t="n">
-        <v>46.46438471635264</v>
+        <v>7.550462516407304</v>
       </c>
       <c r="E16" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F16" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>45.32560226709534</v>
+        <v>7.365410368402993</v>
       </c>
       <c r="D17" t="n">
-        <v>45.26170064058651</v>
+        <v>7.355026354095308</v>
       </c>
       <c r="E17" t="n">
-        <v>12.50170028520865</v>
+        <v>2.031526296346406</v>
       </c>
       <c r="F17" t="n">
-        <v>13.46296140767779</v>
+        <v>2.187731228747641</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
